--- a/databank_toan.xlsx
+++ b/databank_toan.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel\AI_CommentTool_Hasty_Spider\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67434F5C-0991-45DA-8D55-B32A8415CD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB5047F8-F040-43F6-BC58-6AE4BEE0F562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="932" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Toán" sheetId="15" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="203">
   <si>
     <t>STT</t>
   </si>
@@ -624,6 +624,27 @@
   </si>
   <si>
     <t>KHEN TRƯỚC, CHÊ SAU</t>
+  </si>
+  <si>
+    <t>Em nắm chắc kiến thức đã học, tính toán cẩn thận, thực hiện tốt các dạng toán.</t>
+  </si>
+  <si>
+    <t>CK2</t>
+  </si>
+  <si>
+    <t>Em có tư duy toán tốt, vận dụng kiến thức đã học để thực hiện chính xác các bài tập.</t>
+  </si>
+  <si>
+    <t>Em có nhiều tiến bộ trong kĩ năng tính toán, tiếp thu tốt, cần tiếp tục cố gắng rèn luyện.</t>
+  </si>
+  <si>
+    <t>Em tiếp thu kiến thức tốt, tích cực phát biểu xây dựng bài, trình bày cẩn thận, sạch đẹp.</t>
+  </si>
+  <si>
+    <t>Em có tiến bộ, cần tiếp tục cố gắng rèn luyện kĩ năng tính toán và làm bài cẩn thận hơn.</t>
+  </si>
+  <si>
+    <t>Em có tư duy toán tốt, tuy nhiên cần làm bài cẩn thận hơn.</t>
   </si>
 </sst>
 </file>
@@ -658,12 +679,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -708,7 +741,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -741,6 +774,36 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1025,7 +1088,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.4140625" style="2" customWidth="1"/>
@@ -2285,6 +2348,1246 @@
         <v>13</v>
       </c>
     </row>
+    <row r="47" spans="1:9" ht="45" x14ac:dyDescent="0.35">
+      <c r="A47" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A48" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F48" s="15">
+        <v>9</v>
+      </c>
+      <c r="G48" s="10"/>
+      <c r="H48" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A49" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F49" s="18">
+        <v>9</v>
+      </c>
+      <c r="G49" s="16"/>
+      <c r="H49" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A50" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F50" s="18">
+        <v>10</v>
+      </c>
+      <c r="G50" s="16"/>
+      <c r="H50" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A51" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F51" s="15">
+        <v>9</v>
+      </c>
+      <c r="G51" s="10"/>
+      <c r="H51" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I51" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A52" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F52" s="15">
+        <v>10</v>
+      </c>
+      <c r="G52" s="10"/>
+      <c r="H52" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I52" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A53" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D53" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F53" s="15">
+        <v>9</v>
+      </c>
+      <c r="G53" s="10"/>
+      <c r="H53" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I53" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A54" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C54" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D54" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E54" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F54" s="18">
+        <v>10</v>
+      </c>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I54" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A55" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F55" s="15">
+        <v>10</v>
+      </c>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I55" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A56" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F56" s="15">
+        <v>10</v>
+      </c>
+      <c r="G56" s="10"/>
+      <c r="H56" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I56" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A57" s="14">
+        <v>10</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F57" s="20">
+        <v>10</v>
+      </c>
+      <c r="G57" s="19"/>
+      <c r="H57" s="19" t="s">
+        <v>198</v>
+      </c>
+      <c r="I57" s="10"/>
+    </row>
+    <row r="58" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A58" s="14">
+        <v>11</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="F58" s="20">
+        <v>9</v>
+      </c>
+      <c r="G58" s="19"/>
+      <c r="H58" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="I58" s="10"/>
+    </row>
+    <row r="59" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A59" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D59" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F59" s="15">
+        <v>10</v>
+      </c>
+      <c r="G59" s="10"/>
+      <c r="H59" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I59" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A60" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D60" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F60" s="15">
+        <v>10</v>
+      </c>
+      <c r="G60" s="10"/>
+      <c r="H60" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I60" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A61" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D61" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F61" s="15">
+        <v>10</v>
+      </c>
+      <c r="G61" s="10"/>
+      <c r="H61" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I61" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A62" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F62" s="15">
+        <v>10</v>
+      </c>
+      <c r="G62" s="10"/>
+      <c r="H62" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="I62" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A63" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F63" s="15">
+        <v>10</v>
+      </c>
+      <c r="G63" s="10"/>
+      <c r="H63" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I63" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A64" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F64" s="15">
+        <v>10</v>
+      </c>
+      <c r="G64" s="10"/>
+      <c r="H64" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I64" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A65" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D65" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F65" s="15">
+        <v>10</v>
+      </c>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I65" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A66" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F66" s="15">
+        <v>9</v>
+      </c>
+      <c r="G66" s="10"/>
+      <c r="H66" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I66" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A67" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E67" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F67" s="15">
+        <v>10</v>
+      </c>
+      <c r="G67" s="10"/>
+      <c r="H67" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I67" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A68" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B68" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="D68" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="F68" s="18">
+        <v>9</v>
+      </c>
+      <c r="G68" s="16"/>
+      <c r="H68" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I68" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A69" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F69" s="15">
+        <v>9</v>
+      </c>
+      <c r="G69" s="10"/>
+      <c r="H69" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A70" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D70" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="E70" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F70" s="15">
+        <v>10</v>
+      </c>
+      <c r="G70" s="10"/>
+      <c r="H70" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A71" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F71" s="15">
+        <v>9</v>
+      </c>
+      <c r="G71" s="10"/>
+      <c r="H71" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A72" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="B72" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="E72" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F72" s="15">
+        <v>10</v>
+      </c>
+      <c r="G72" s="10"/>
+      <c r="H72" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A73" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F73" s="15">
+        <v>10</v>
+      </c>
+      <c r="G73" s="10"/>
+      <c r="H73" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A74" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="D74" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F74" s="15">
+        <v>10</v>
+      </c>
+      <c r="G74" s="10"/>
+      <c r="H74" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I74" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A75" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D75" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F75" s="15">
+        <v>10</v>
+      </c>
+      <c r="G75" s="10"/>
+      <c r="H75" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A76" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D76" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F76" s="15">
+        <v>9</v>
+      </c>
+      <c r="G76" s="10"/>
+      <c r="H76" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A77" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="D77" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F77" s="15">
+        <v>10</v>
+      </c>
+      <c r="G77" s="10"/>
+      <c r="H77" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A78" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D78" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F78" s="15">
+        <v>10</v>
+      </c>
+      <c r="G78" s="10"/>
+      <c r="H78" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A79" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="D79" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F79" s="15">
+        <v>10</v>
+      </c>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I79" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A80" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F80" s="15">
+        <v>9</v>
+      </c>
+      <c r="G80" s="10"/>
+      <c r="H80" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I80" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A81" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D81" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F81" s="15">
+        <v>10</v>
+      </c>
+      <c r="G81" s="10"/>
+      <c r="H81" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A82" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="D82" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F82" s="15">
+        <v>9</v>
+      </c>
+      <c r="G82" s="10"/>
+      <c r="H82" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A83" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F83" s="15">
+        <v>10</v>
+      </c>
+      <c r="G83" s="10"/>
+      <c r="H83" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I83" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A84" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F84" s="15">
+        <v>10</v>
+      </c>
+      <c r="G84" s="10"/>
+      <c r="H84" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I84" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A85" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F85" s="15">
+        <v>8</v>
+      </c>
+      <c r="G85" s="10"/>
+      <c r="H85" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="I85" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A86" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F86" s="15">
+        <v>10</v>
+      </c>
+      <c r="G86" s="10"/>
+      <c r="H86" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I86" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A87" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="D87" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F87" s="15">
+        <v>10</v>
+      </c>
+      <c r="G87" s="10"/>
+      <c r="H87" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A88" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="B88" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D88" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F88" s="15">
+        <v>10</v>
+      </c>
+      <c r="G88" s="10"/>
+      <c r="H88" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="I88" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A89" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="D89" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="F89" s="15">
+        <v>8</v>
+      </c>
+      <c r="G89" s="10"/>
+      <c r="H89" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A90" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="D90" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F90" s="15">
+        <v>10</v>
+      </c>
+      <c r="G90" s="10"/>
+      <c r="H90" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="I90" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A91" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F91" s="15">
+        <v>10</v>
+      </c>
+      <c r="G91" s="10"/>
+      <c r="H91" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="I91" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="28" x14ac:dyDescent="0.35">
+      <c r="A92" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="F92" s="15">
+        <v>10</v>
+      </c>
+      <c r="G92" s="10"/>
+      <c r="H92" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I92" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0"/>
